--- a/Team-Data/2013-14/3-11-2013-14.xlsx
+++ b/Team-Data/2013-14/3-11-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -769,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
         <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>19.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.324</v>
+        <v>0.327</v>
       </c>
       <c r="O3" t="n">
         <v>16.3</v>
@@ -882,22 +949,22 @@
         <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="T3" t="n">
         <v>43</v>
       </c>
       <c r="U3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W3" t="n">
         <v>7.2</v>
@@ -909,19 +976,19 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
         <v>19.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -936,7 +1003,7 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>11</v>
@@ -954,16 +1021,16 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
@@ -975,7 +1042,7 @@
         <v>24</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
         <v>22</v>
@@ -993,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
@@ -1127,7 +1194,7 @@
         <v>14</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM4" t="n">
         <v>11</v>
@@ -1139,13 +1206,13 @@
         <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1309,7 +1376,7 @@
         <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1357,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.547</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1407,7 +1474,7 @@
         <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.431</v>
@@ -1419,25 +1486,25 @@
         <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
         <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R6" t="n">
         <v>11.9</v>
       </c>
       <c r="S6" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T6" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U6" t="n">
         <v>22.2</v>
@@ -1458,16 +1525,16 @@
         <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1488,10 +1555,10 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1524,10 +1591,10 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1661,13 +1728,13 @@
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -1753,46 +1820,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
         <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.585</v>
+        <v>0.594</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
         <v>83.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
         <v>8.4</v>
       </c>
       <c r="M8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.796</v>
+        <v>0.8</v>
       </c>
       <c r="R8" t="n">
         <v>10.1</v>
@@ -1804,13 +1871,13 @@
         <v>40.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W8" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>4.2</v>
@@ -1819,31 +1886,31 @@
         <v>3.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA8" t="n">
         <v>19.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.2</v>
+        <v>104.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1855,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
         <v>18</v>
@@ -1894,10 +1961,10 @@
         <v>23</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2070,7 +2137,7 @@
         <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2184,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
         <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>0.391</v>
+        <v>0.381</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J10" t="n">
         <v>86.8</v>
@@ -2141,37 +2208,37 @@
         <v>0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M10" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="O10" t="n">
         <v>17.3</v>
       </c>
       <c r="P10" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.673</v>
+        <v>0.671</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T10" t="n">
         <v>45.1</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
         <v>8.699999999999999</v>
@@ -2183,7 +2250,7 @@
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA10" t="n">
         <v>20.6</v>
@@ -2192,22 +2259,22 @@
         <v>100.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>8</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2255,7 +2322,7 @@
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -2299,52 +2366,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.631</v>
+        <v>0.625</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M11" t="n">
         <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O11" t="n">
         <v>16.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R11" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T11" t="n">
         <v>45.5</v>
@@ -2362,22 +2429,22 @@
         <v>5.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
@@ -2407,13 +2474,13 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>23</v>
@@ -2425,16 +2492,16 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="n">
         <v>8</v>
@@ -2443,16 +2510,16 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
         <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.698</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L12" t="n">
         <v>9.199999999999999</v>
@@ -2517,7 +2584,7 @@
         <v>21.7</v>
       </c>
       <c r="P12" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0.697</v>
@@ -2526,7 +2593,7 @@
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T12" t="n">
         <v>45.2</v>
@@ -2535,7 +2602,7 @@
         <v>20.8</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.5</v>
@@ -2544,7 +2611,7 @@
         <v>5.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
         <v>20.2</v>
@@ -2553,13 +2620,13 @@
         <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.5</v>
+        <v>106.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2568,13 +2635,13 @@
         <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,10 +2748,10 @@
         <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
@@ -2693,13 +2760,13 @@
         <v>19.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q13" t="n">
         <v>0.783</v>
@@ -2711,7 +2778,7 @@
         <v>34.9</v>
       </c>
       <c r="T13" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U13" t="n">
         <v>20.3</v>
@@ -2723,7 +2790,7 @@
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y13" t="n">
         <v>4.5</v>
@@ -2735,13 +2802,13 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,13 +2820,13 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>13</v>
@@ -2771,13 +2838,13 @@
         <v>24</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2789,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
@@ -2801,13 +2868,13 @@
         <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -2929,10 +2996,10 @@
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>14</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
@@ -3159,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.587</v>
+        <v>0.581</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
         <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L16" t="n">
         <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R16" t="n">
         <v>11.4</v>
@@ -3260,10 +3327,10 @@
         <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W16" t="n">
         <v>7.7</v>
@@ -3281,13 +3348,13 @@
         <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3296,19 +3363,19 @@
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3338,7 +3405,7 @@
         <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3572,7 @@
         <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3523,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -3573,64 +3640,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>0.203</v>
+        <v>0.206</v>
       </c>
       <c r="H18" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
       </c>
       <c r="M18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O18" t="n">
         <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="R18" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S18" t="n">
         <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V18" t="n">
         <v>15.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X18" t="n">
         <v>5.2</v>
@@ -3639,19 +3706,19 @@
         <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>-8</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,16 +3730,16 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
@@ -3684,16 +3751,16 @@
         <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3711,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3720,7 +3787,7 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
         <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,19 +3840,19 @@
         <v>38.6</v>
       </c>
       <c r="J19" t="n">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>7.4</v>
       </c>
       <c r="M19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O19" t="n">
         <v>21.7</v>
@@ -3794,25 +3861,25 @@
         <v>27.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
         <v>12.9</v>
       </c>
       <c r="S19" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T19" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X19" t="n">
         <v>3.5</v>
@@ -3821,22 +3888,22 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
         <v>23.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -3878,13 +3945,13 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4069,10 +4136,10 @@
         <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4084,13 +4151,13 @@
         <v>28</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
         <v>19</v>
       </c>
       <c r="BC20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4273,7 @@
         <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>8</v>
@@ -4224,7 +4291,7 @@
         <v>5</v>
       </c>
       <c r="AM21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN21" t="n">
         <v>11</v>
@@ -4260,7 +4327,7 @@
         <v>18</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J22" t="n">
         <v>82.5</v>
@@ -4328,37 +4395,37 @@
         <v>7.7</v>
       </c>
       <c r="M22" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N22" t="n">
         <v>0.359</v>
       </c>
       <c r="O22" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P22" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q22" t="n">
         <v>0.803</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S22" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T22" t="n">
         <v>45.2</v>
       </c>
       <c r="U22" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
         <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X22" t="n">
         <v>6.1</v>
@@ -4367,19 +4434,19 @@
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
         <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.8</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
@@ -4415,28 +4482,28 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4679,7 @@
         <v>20</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4621,7 +4688,7 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI24" t="n">
         <v>12</v>
@@ -4785,10 +4852,10 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>2.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF25" t="n">
         <v>11</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>10</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4946,16 +5013,16 @@
         <v>10</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
       </c>
       <c r="AM25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4964,7 +5031,7 @@
         <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -5029,67 +5096,67 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="n">
         <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>0.656</v>
+        <v>0.667</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J26" t="n">
         <v>87.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L26" t="n">
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.821</v>
       </c>
       <c r="R26" t="n">
         <v>12.8</v>
       </c>
       <c r="S26" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="T26" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="U26" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W26" t="n">
         <v>5.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
@@ -5098,16 +5165,16 @@
         <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.5</v>
+        <v>107.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5134,16 +5201,16 @@
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5158,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
         <v>82.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O27" t="n">
         <v>20.7</v>
@@ -5250,7 +5317,7 @@
         <v>26.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.768</v>
+        <v>0.771</v>
       </c>
       <c r="R27" t="n">
         <v>12.1</v>
@@ -5259,7 +5326,7 @@
         <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U27" t="n">
         <v>19.1</v>
@@ -5274,22 +5341,22 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
         <v>23.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.1</v>
+        <v>101.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,13 +5368,13 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
         <v>18</v>
@@ -5328,13 +5395,13 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
         <v>19</v>
@@ -5364,7 +5431,7 @@
         <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5411,28 +5478,28 @@
         <v>40.2</v>
       </c>
       <c r="J28" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.489</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
         <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.395</v>
+        <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="R28" t="n">
         <v>8.9</v>
@@ -5441,7 +5508,7 @@
         <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U28" t="n">
         <v>25</v>
@@ -5450,7 +5517,7 @@
         <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
@@ -5459,7 +5526,7 @@
         <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="AA28" t="n">
         <v>19.7</v>
@@ -5471,7 +5538,7 @@
         <v>6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
         <v>28</v>
@@ -5513,25 +5580,25 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -5677,7 +5744,7 @@
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -5835,25 +5902,25 @@
         <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
@@ -5871,7 +5938,7 @@
         <v>22</v>
       </c>
       <c r="AP30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ30" t="n">
         <v>21</v>
@@ -5880,7 +5947,7 @@
         <v>19</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>23</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6059,16 +6126,16 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>13</v>
@@ -6092,7 +6159,7 @@
         <v>16</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-11-2013-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
     </row>
